--- a/AAII_Financials/Yearly/IMAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IMAB_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -656,52 +656,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -714,33 +714,36 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>12200</v>
       </c>
-      <c r="F8" s="3">
-        <v>213000</v>
-      </c>
       <c r="G8" s="3">
-        <v>4100</v>
+        <v>214500</v>
       </c>
       <c r="H8" s="3">
-        <v>7400</v>
+        <v>4200</v>
       </c>
       <c r="I8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J8" s="3">
         <v>1600</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -753,20 +756,23 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
         <v>3800</v>
       </c>
-      <c r="E9" s="3">
-        <v>6400</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
+      <c r="F9" s="3">
+        <v>6500</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -792,20 +798,23 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3">
-        <v>5700</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5800</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -831,9 +840,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,31 +861,32 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>124900</v>
+        <v>112700</v>
       </c>
       <c r="E12" s="3">
-        <v>167500</v>
+        <v>125800</v>
       </c>
       <c r="F12" s="3">
-        <v>136000</v>
+        <v>168600</v>
       </c>
       <c r="G12" s="3">
-        <v>116000</v>
+        <v>136900</v>
       </c>
       <c r="H12" s="3">
-        <v>58800</v>
+        <v>116800</v>
       </c>
       <c r="I12" s="3">
-        <v>36900</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+        <v>59200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>37100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -887,9 +900,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,27 +942,30 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>-56300</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>-56700</v>
+      </c>
+      <c r="H14" s="3">
         <v>3200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -962,12 +981,15 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1004,9 +1026,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,31 +1044,32 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>241400</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E17" s="3">
-        <v>298200</v>
+        <v>243000</v>
       </c>
       <c r="F17" s="3">
-        <v>135200</v>
+        <v>300200</v>
       </c>
       <c r="G17" s="3">
-        <v>209600</v>
+        <v>136200</v>
       </c>
       <c r="H17" s="3">
-        <v>68000</v>
+        <v>211000</v>
       </c>
       <c r="I17" s="3">
-        <v>40400</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>68500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>40700</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1057,32 +1083,35 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E18" s="3">
-        <v>-286000</v>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F18" s="3">
-        <v>77800</v>
+        <v>-288000</v>
       </c>
       <c r="G18" s="3">
-        <v>-205500</v>
+        <v>78300</v>
       </c>
       <c r="H18" s="3">
-        <v>-60600</v>
+        <v>-206900</v>
       </c>
       <c r="I18" s="3">
-        <v>-38800</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-61000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-39100</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1096,9 +1125,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,32 +1146,33 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>-36400</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>-10900</v>
+        <v>-36600</v>
       </c>
       <c r="G20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="H20" s="3">
         <v>5400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1600</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1152,29 +1185,32 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>-342500</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>-320400</v>
+        <v>-346400</v>
       </c>
       <c r="F21" s="3">
-        <v>68800</v>
+        <v>-322600</v>
       </c>
       <c r="G21" s="3">
-        <v>-198700</v>
+        <v>68700</v>
       </c>
       <c r="H21" s="3">
-        <v>-52800</v>
+        <v>-200500</v>
       </c>
       <c r="I21" s="3">
-        <v>-40200</v>
+        <v>-53900</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1191,33 +1227,36 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,32 +1269,35 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-346100</v>
+        <v>-203800</v>
       </c>
       <c r="E23" s="3">
-        <v>-322400</v>
+        <v>-348500</v>
       </c>
       <c r="F23" s="3">
-        <v>66700</v>
+        <v>-324600</v>
       </c>
       <c r="G23" s="3">
-        <v>-200500</v>
+        <v>67200</v>
       </c>
       <c r="H23" s="3">
-        <v>-55400</v>
+        <v>-201900</v>
       </c>
       <c r="I23" s="3">
-        <v>-41200</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>-55800</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-41500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1269,32 +1311,35 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1700</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1308,9 +1353,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,32 +1395,35 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-346200</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E26" s="3">
-        <v>-321900</v>
+        <v>-348600</v>
       </c>
       <c r="F26" s="3">
-        <v>65000</v>
+        <v>-324100</v>
       </c>
       <c r="G26" s="3">
-        <v>-200500</v>
+        <v>65500</v>
       </c>
       <c r="H26" s="3">
-        <v>-55600</v>
+        <v>-201900</v>
       </c>
       <c r="I26" s="3">
-        <v>-41200</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>-56000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-41500</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1386,32 +1437,35 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-346200</v>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E27" s="3">
-        <v>-321900</v>
+        <v>-348600</v>
       </c>
       <c r="F27" s="3">
-        <v>65000</v>
+        <v>-324100</v>
       </c>
       <c r="G27" s="3">
-        <v>-205000</v>
+        <v>65500</v>
       </c>
       <c r="H27" s="3">
-        <v>-55600</v>
+        <v>-206400</v>
       </c>
       <c r="I27" s="3">
-        <v>-41200</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>-56000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-41500</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1425,9 +1479,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,33 +1647,36 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>36400</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>10900</v>
+        <v>36600</v>
       </c>
       <c r="G32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-5400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1600</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1620,32 +1689,35 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-346200</v>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E33" s="3">
-        <v>-321900</v>
+        <v>-348600</v>
       </c>
       <c r="F33" s="3">
-        <v>65000</v>
+        <v>-324100</v>
       </c>
       <c r="G33" s="3">
-        <v>-205000</v>
+        <v>65500</v>
       </c>
       <c r="H33" s="3">
-        <v>-55600</v>
+        <v>-206400</v>
       </c>
       <c r="I33" s="3">
-        <v>-41200</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>-56000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-41500</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1659,9 +1731,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,32 +1773,35 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-346200</v>
+      <c r="D35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E35" s="3">
-        <v>-321900</v>
+        <v>-348600</v>
       </c>
       <c r="F35" s="3">
-        <v>65000</v>
+        <v>-324100</v>
       </c>
       <c r="G35" s="3">
-        <v>-205000</v>
+        <v>65500</v>
       </c>
       <c r="H35" s="3">
-        <v>-55600</v>
+        <v>-206400</v>
       </c>
       <c r="I35" s="3">
-        <v>-41200</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>-56000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-41500</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1737,38 +1815,41 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1781,9 +1862,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,31 +1901,32 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>443800</v>
+        <v>297700</v>
       </c>
       <c r="E41" s="3">
-        <v>486500</v>
+        <v>446800</v>
       </c>
       <c r="F41" s="3">
-        <v>657100</v>
+        <v>489900</v>
       </c>
       <c r="G41" s="3">
-        <v>157100</v>
+        <v>661600</v>
       </c>
       <c r="H41" s="3">
-        <v>219300</v>
+        <v>158100</v>
       </c>
       <c r="I41" s="3">
-        <v>42500</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>220800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>42800</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1854,32 +1940,35 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>32500</v>
+        <v>19900</v>
       </c>
       <c r="E42" s="3">
-        <v>104000</v>
+        <v>32700</v>
       </c>
       <c r="F42" s="3">
-        <v>4400</v>
+        <v>104700</v>
       </c>
       <c r="G42" s="3">
         <v>4400</v>
       </c>
       <c r="H42" s="3">
-        <v>29800</v>
+        <v>4400</v>
       </c>
       <c r="I42" s="3">
-        <v>36800</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>30000</v>
+      </c>
+      <c r="J42" s="3">
+        <v>37000</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1893,33 +1982,36 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>1100</v>
       </c>
-      <c r="E43" s="3">
-        <v>52000</v>
-      </c>
       <c r="F43" s="3">
-        <v>61200</v>
+        <v>52300</v>
       </c>
       <c r="G43" s="3">
+        <v>61600</v>
+      </c>
+      <c r="H43" s="3">
         <v>4100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1932,21 +2024,24 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
         <v>3800</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1962,8 +2057,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -1971,32 +2066,35 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>23300</v>
+        <v>7200</v>
       </c>
       <c r="E45" s="3">
-        <v>14000</v>
+        <v>23500</v>
       </c>
       <c r="F45" s="3">
-        <v>15200</v>
+        <v>14100</v>
       </c>
       <c r="G45" s="3">
-        <v>22400</v>
+        <v>15300</v>
       </c>
       <c r="H45" s="3">
-        <v>24300</v>
+        <v>22600</v>
       </c>
       <c r="I45" s="3">
-        <v>15700</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>24500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>15800</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2010,32 +2108,35 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>500700</v>
+        <v>324800</v>
       </c>
       <c r="E46" s="3">
-        <v>660300</v>
+        <v>504200</v>
       </c>
       <c r="F46" s="3">
-        <v>737900</v>
+        <v>664800</v>
       </c>
       <c r="G46" s="3">
-        <v>188000</v>
+        <v>742900</v>
       </c>
       <c r="H46" s="3">
-        <v>281200</v>
+        <v>189300</v>
       </c>
       <c r="I46" s="3">
-        <v>95500</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>283200</v>
+      </c>
+      <c r="J46" s="3">
+        <v>96100</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2049,23 +2150,26 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E47" s="3">
         <v>4300</v>
       </c>
-      <c r="E47" s="3">
-        <v>48600</v>
-      </c>
       <c r="F47" s="3">
-        <v>91800</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+        <v>48900</v>
+      </c>
+      <c r="G47" s="3">
+        <v>92400</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2082,39 +2186,42 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17100</v>
+        <v>11500</v>
       </c>
       <c r="E48" s="3">
-        <v>21900</v>
+        <v>17200</v>
       </c>
       <c r="F48" s="3">
+        <v>22000</v>
+      </c>
+      <c r="G48" s="3">
         <v>5600</v>
       </c>
-      <c r="G48" s="3">
-        <v>6400</v>
-      </c>
       <c r="H48" s="3">
+        <v>6500</v>
+      </c>
+      <c r="I48" s="3">
         <v>3800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2127,32 +2234,35 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>38900</v>
+        <v>16400</v>
       </c>
       <c r="E49" s="3">
-        <v>39000</v>
+        <v>39100</v>
       </c>
       <c r="F49" s="3">
-        <v>39100</v>
+        <v>39200</v>
       </c>
       <c r="G49" s="3">
-        <v>43000</v>
+        <v>39300</v>
       </c>
       <c r="H49" s="3">
-        <v>43000</v>
+        <v>43300</v>
       </c>
       <c r="I49" s="3">
-        <v>43000</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>43300</v>
+      </c>
+      <c r="J49" s="3">
+        <v>43300</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2166,9 +2276,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,27 +2360,30 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E52" s="3">
         <v>1500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2500</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2280,12 +2399,15 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,32 +2444,35 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>562500</v>
+        <v>363300</v>
       </c>
       <c r="E54" s="3">
-        <v>773400</v>
+        <v>566300</v>
       </c>
       <c r="F54" s="3">
-        <v>874600</v>
+        <v>778700</v>
       </c>
       <c r="G54" s="3">
-        <v>239900</v>
+        <v>880500</v>
       </c>
       <c r="H54" s="3">
-        <v>328100</v>
+        <v>241600</v>
       </c>
       <c r="I54" s="3">
-        <v>141600</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>330300</v>
+      </c>
+      <c r="J54" s="3">
+        <v>142500</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2361,9 +2486,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,19 +2525,20 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3">
-        <v>7900</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3">
+        <v>8000</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2425,8 +2555,8 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2434,32 +2564,35 @@
       <c r="N57" s="3">
         <v>0</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2600</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="I58" s="3">
-        <v>13700</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>11100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>13800</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2473,32 +2606,35 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>102100</v>
+        <v>3300</v>
       </c>
       <c r="E59" s="3">
-        <v>78200</v>
+        <v>102800</v>
       </c>
       <c r="F59" s="3">
-        <v>79600</v>
+        <v>78800</v>
       </c>
       <c r="G59" s="3">
-        <v>74400</v>
+        <v>80100</v>
       </c>
       <c r="H59" s="3">
-        <v>36800</v>
+        <v>74900</v>
       </c>
       <c r="I59" s="3">
-        <v>13300</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>37000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>13400</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2512,32 +2648,35 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>104700</v>
+        <v>57300</v>
       </c>
       <c r="E60" s="3">
-        <v>86200</v>
+        <v>105400</v>
       </c>
       <c r="F60" s="3">
-        <v>79600</v>
+        <v>86700</v>
       </c>
       <c r="G60" s="3">
-        <v>81300</v>
+        <v>80100</v>
       </c>
       <c r="H60" s="3">
-        <v>47800</v>
+        <v>81800</v>
       </c>
       <c r="I60" s="3">
-        <v>26900</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>48100</v>
+      </c>
+      <c r="J60" s="3">
+        <v>27100</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2551,9 +2690,12 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2567,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>9400</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I61" s="3">
         <v>9300</v>
       </c>
-      <c r="I61" s="3">
-        <v>15700</v>
-      </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>15800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2590,32 +2732,35 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>56000</v>
+        <v>67100</v>
       </c>
       <c r="E62" s="3">
-        <v>57700</v>
+        <v>56400</v>
       </c>
       <c r="F62" s="3">
-        <v>18000</v>
+        <v>58100</v>
       </c>
       <c r="G62" s="3">
+        <v>18100</v>
+      </c>
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>300</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2629,9 +2774,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,32 +2900,35 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>160700</v>
+        <v>124400</v>
       </c>
       <c r="E66" s="3">
-        <v>143800</v>
+        <v>161800</v>
       </c>
       <c r="F66" s="3">
-        <v>97600</v>
+        <v>144800</v>
       </c>
       <c r="G66" s="3">
-        <v>92200</v>
+        <v>98200</v>
       </c>
       <c r="H66" s="3">
-        <v>57400</v>
+        <v>92900</v>
       </c>
       <c r="I66" s="3">
-        <v>84900</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>57800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>85500</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2785,9 +2942,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2896,16 +3063,16 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>428600</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>402600</v>
+        <v>431500</v>
       </c>
       <c r="I70" s="3">
-        <v>98100</v>
+        <v>405300</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>98700</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,32 +3128,35 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-947500</v>
+        <v>-1157700</v>
       </c>
       <c r="E72" s="3">
-        <v>-601300</v>
+        <v>-954000</v>
       </c>
       <c r="F72" s="3">
-        <v>-279400</v>
+        <v>-605400</v>
       </c>
       <c r="G72" s="3">
-        <v>-344400</v>
+        <v>-281300</v>
       </c>
       <c r="H72" s="3">
-        <v>-140100</v>
+        <v>-346700</v>
       </c>
       <c r="I72" s="3">
-        <v>-49400</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>-141000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-49700</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2997,9 +3170,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,32 +3296,35 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>401800</v>
+        <v>238900</v>
       </c>
       <c r="E76" s="3">
-        <v>629600</v>
+        <v>404500</v>
       </c>
       <c r="F76" s="3">
-        <v>777000</v>
+        <v>633900</v>
       </c>
       <c r="G76" s="3">
-        <v>-280900</v>
+        <v>782300</v>
       </c>
       <c r="H76" s="3">
-        <v>-131900</v>
+        <v>-282800</v>
       </c>
       <c r="I76" s="3">
-        <v>-41400</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>-132800</v>
+      </c>
+      <c r="J76" s="3">
+        <v>-41600</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3153,9 +3338,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,38 +3380,41 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3236,32 +3427,35 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-346200</v>
+      <c r="D81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E81" s="3">
-        <v>-321900</v>
+        <v>-348600</v>
       </c>
       <c r="F81" s="3">
-        <v>65000</v>
+        <v>-324100</v>
       </c>
       <c r="G81" s="3">
-        <v>-205000</v>
+        <v>65500</v>
       </c>
       <c r="H81" s="3">
-        <v>-55600</v>
+        <v>-206400</v>
       </c>
       <c r="I81" s="3">
-        <v>-41200</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>-56000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-41500</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3275,9 +3469,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,32 +3490,33 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>3600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2000</v>
       </c>
       <c r="F83" s="3">
         <v>2000</v>
       </c>
       <c r="G83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H83" s="3">
         <v>1400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3331,9 +3529,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,32 +3739,35 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-152300</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E89" s="3">
-        <v>-134400</v>
+        <v>-153300</v>
       </c>
       <c r="F89" s="3">
-        <v>59900</v>
+        <v>-135300</v>
       </c>
       <c r="G89" s="3">
-        <v>-119900</v>
+        <v>60300</v>
       </c>
       <c r="H89" s="3">
-        <v>-38800</v>
+        <v>-120700</v>
       </c>
       <c r="I89" s="3">
-        <v>-34800</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>-39000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-35100</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3565,9 +3781,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,32 +3802,33 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-6300</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>-4100</v>
+        <v>-6400</v>
       </c>
       <c r="F91" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2800</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,9 +3841,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,32 +3925,35 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>63300</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
-        <v>-100400</v>
+        <v>63700</v>
       </c>
       <c r="F94" s="3">
-        <v>-27900</v>
+        <v>-101100</v>
       </c>
       <c r="G94" s="3">
-        <v>29300</v>
+        <v>-28100</v>
       </c>
       <c r="H94" s="3">
+        <v>29500</v>
+      </c>
+      <c r="I94" s="3">
         <v>1300</v>
       </c>
-      <c r="I94" s="3">
-        <v>-21800</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>-21900</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3738,9 +3967,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,8 +3988,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,32 +4153,35 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>5800</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
-        <v>82000</v>
+        <v>5900</v>
       </c>
       <c r="F100" s="3">
-        <v>475100</v>
+        <v>82600</v>
       </c>
       <c r="G100" s="3">
-        <v>21100</v>
+        <v>478300</v>
       </c>
       <c r="H100" s="3">
-        <v>204300</v>
+        <v>21200</v>
       </c>
       <c r="I100" s="3">
-        <v>104700</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>205700</v>
+      </c>
+      <c r="J100" s="3">
+        <v>105500</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3950,32 +4195,35 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>53700</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E101" s="3">
-        <v>-17800</v>
+        <v>54100</v>
       </c>
       <c r="F101" s="3">
-        <v>-14700</v>
+        <v>-17900</v>
       </c>
       <c r="G101" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="H101" s="3">
         <v>2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8300</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3989,32 +4237,35 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>-29400</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E102" s="3">
-        <v>-170500</v>
+        <v>-29600</v>
       </c>
       <c r="F102" s="3">
-        <v>492300</v>
+        <v>-171700</v>
       </c>
       <c r="G102" s="3">
-        <v>-67300</v>
+        <v>495700</v>
       </c>
       <c r="H102" s="3">
-        <v>175100</v>
+        <v>-67800</v>
       </c>
       <c r="I102" s="3">
-        <v>48100</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>176300</v>
+      </c>
+      <c r="J102" s="3">
+        <v>48500</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
@@ -4028,7 +4279,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/IMAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IMAB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -733,13 +733,13 @@
         <v>12200</v>
       </c>
       <c r="G8" s="3">
-        <v>214500</v>
+        <v>213100</v>
       </c>
       <c r="H8" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="I8" s="3">
-        <v>7500</v>
+        <v>7400</v>
       </c>
       <c r="J8" s="3">
         <v>1600</v>
@@ -772,7 +772,7 @@
         <v>3800</v>
       </c>
       <c r="F9" s="3">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -814,7 +814,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -868,25 +868,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>112700</v>
+        <v>112000</v>
       </c>
       <c r="E12" s="3">
-        <v>125800</v>
+        <v>125000</v>
       </c>
       <c r="F12" s="3">
-        <v>168600</v>
+        <v>167600</v>
       </c>
       <c r="G12" s="3">
-        <v>136900</v>
+        <v>136000</v>
       </c>
       <c r="H12" s="3">
-        <v>116800</v>
+        <v>116100</v>
       </c>
       <c r="I12" s="3">
-        <v>59200</v>
+        <v>58900</v>
       </c>
       <c r="J12" s="3">
-        <v>37100</v>
+        <v>36900</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -951,8 +951,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>23600</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>-56700</v>
+        <v>-56300</v>
       </c>
       <c r="H14" s="3">
         <v>3200</v>
@@ -1050,26 +1050,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>198100</v>
       </c>
       <c r="E17" s="3">
-        <v>243000</v>
+        <v>241500</v>
       </c>
       <c r="F17" s="3">
-        <v>300200</v>
+        <v>298300</v>
       </c>
       <c r="G17" s="3">
-        <v>136200</v>
+        <v>135300</v>
       </c>
       <c r="H17" s="3">
-        <v>211000</v>
+        <v>209700</v>
       </c>
       <c r="I17" s="3">
-        <v>68500</v>
+        <v>68000</v>
       </c>
       <c r="J17" s="3">
-        <v>40700</v>
+        <v>40400</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1092,26 +1092,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-194300</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="3">
-        <v>-288000</v>
+        <v>-286200</v>
       </c>
       <c r="G18" s="3">
-        <v>78300</v>
+        <v>77800</v>
       </c>
       <c r="H18" s="3">
-        <v>-206900</v>
+        <v>-205600</v>
       </c>
       <c r="I18" s="3">
-        <v>-61000</v>
+        <v>-60600</v>
       </c>
       <c r="J18" s="3">
-        <v>-39100</v>
+        <v>-38800</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1152,17 +1152,17 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-8100</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>-36600</v>
+        <v>-36400</v>
       </c>
       <c r="G20" s="3">
-        <v>-11000</v>
+        <v>-10900</v>
       </c>
       <c r="H20" s="3">
         <v>5400</v>
@@ -1194,26 +1194,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-199000</v>
       </c>
       <c r="E21" s="3">
-        <v>-346400</v>
+        <v>-342700</v>
       </c>
       <c r="F21" s="3">
-        <v>-322600</v>
+        <v>-320600</v>
       </c>
       <c r="G21" s="3">
-        <v>68700</v>
+        <v>68900</v>
       </c>
       <c r="H21" s="3">
-        <v>-200500</v>
+        <v>-198800</v>
       </c>
       <c r="I21" s="3">
-        <v>-53900</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-52900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-40200</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-203800</v>
+        <v>-202500</v>
       </c>
       <c r="E23" s="3">
-        <v>-348500</v>
+        <v>-346300</v>
       </c>
       <c r="F23" s="3">
-        <v>-324600</v>
+        <v>-322600</v>
       </c>
       <c r="G23" s="3">
-        <v>67200</v>
+        <v>66800</v>
       </c>
       <c r="H23" s="3">
-        <v>-201900</v>
+        <v>-200600</v>
       </c>
       <c r="I23" s="3">
-        <v>-55800</v>
+        <v>-55400</v>
       </c>
       <c r="J23" s="3">
-        <v>-41500</v>
+        <v>-41200</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1404,26 +1404,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-202500</v>
       </c>
       <c r="E26" s="3">
-        <v>-348600</v>
+        <v>-346400</v>
       </c>
       <c r="F26" s="3">
-        <v>-324100</v>
+        <v>-322100</v>
       </c>
       <c r="G26" s="3">
-        <v>65500</v>
+        <v>65100</v>
       </c>
       <c r="H26" s="3">
-        <v>-201900</v>
+        <v>-200600</v>
       </c>
       <c r="I26" s="3">
-        <v>-56000</v>
+        <v>-55700</v>
       </c>
       <c r="J26" s="3">
-        <v>-41500</v>
+        <v>-41200</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1446,26 +1446,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-202500</v>
       </c>
       <c r="E27" s="3">
-        <v>-348600</v>
+        <v>-346400</v>
       </c>
       <c r="F27" s="3">
-        <v>-324100</v>
+        <v>-322100</v>
       </c>
       <c r="G27" s="3">
-        <v>65500</v>
+        <v>65100</v>
       </c>
       <c r="H27" s="3">
-        <v>-206400</v>
+        <v>-205200</v>
       </c>
       <c r="I27" s="3">
-        <v>-56000</v>
+        <v>-55700</v>
       </c>
       <c r="J27" s="3">
-        <v>-41500</v>
+        <v>-41200</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1656,17 +1656,17 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>8100</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>36600</v>
+        <v>36400</v>
       </c>
       <c r="G32" s="3">
-        <v>11000</v>
+        <v>10900</v>
       </c>
       <c r="H32" s="3">
         <v>-5400</v>
@@ -1698,26 +1698,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-202500</v>
       </c>
       <c r="E33" s="3">
-        <v>-348600</v>
+        <v>-346400</v>
       </c>
       <c r="F33" s="3">
-        <v>-324100</v>
+        <v>-322100</v>
       </c>
       <c r="G33" s="3">
-        <v>65500</v>
+        <v>65100</v>
       </c>
       <c r="H33" s="3">
-        <v>-206400</v>
+        <v>-205200</v>
       </c>
       <c r="I33" s="3">
-        <v>-56000</v>
+        <v>-55700</v>
       </c>
       <c r="J33" s="3">
-        <v>-41500</v>
+        <v>-41200</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1782,26 +1782,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-202500</v>
       </c>
       <c r="E35" s="3">
-        <v>-348600</v>
+        <v>-346400</v>
       </c>
       <c r="F35" s="3">
-        <v>-324100</v>
+        <v>-322100</v>
       </c>
       <c r="G35" s="3">
-        <v>65500</v>
+        <v>65100</v>
       </c>
       <c r="H35" s="3">
-        <v>-206400</v>
+        <v>-205200</v>
       </c>
       <c r="I35" s="3">
-        <v>-56000</v>
+        <v>-55700</v>
       </c>
       <c r="J35" s="3">
-        <v>-41500</v>
+        <v>-41200</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>297700</v>
+        <v>295900</v>
       </c>
       <c r="E41" s="3">
-        <v>446800</v>
+        <v>444000</v>
       </c>
       <c r="F41" s="3">
-        <v>489900</v>
+        <v>486800</v>
       </c>
       <c r="G41" s="3">
-        <v>661600</v>
+        <v>657500</v>
       </c>
       <c r="H41" s="3">
-        <v>158100</v>
+        <v>157200</v>
       </c>
       <c r="I41" s="3">
-        <v>220800</v>
+        <v>219400</v>
       </c>
       <c r="J41" s="3">
-        <v>42800</v>
+        <v>42500</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1950,13 +1950,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>19900</v>
+        <v>19800</v>
       </c>
       <c r="E42" s="3">
-        <v>32700</v>
+        <v>32500</v>
       </c>
       <c r="F42" s="3">
-        <v>104700</v>
+        <v>104100</v>
       </c>
       <c r="G42" s="3">
         <v>4400</v>
@@ -1965,10 +1965,10 @@
         <v>4400</v>
       </c>
       <c r="I42" s="3">
-        <v>30000</v>
+        <v>29800</v>
       </c>
       <c r="J42" s="3">
-        <v>37000</v>
+        <v>36800</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1991,17 +1991,17 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>600</v>
       </c>
       <c r="E43" s="3">
         <v>1100</v>
       </c>
       <c r="F43" s="3">
-        <v>52300</v>
+        <v>52000</v>
       </c>
       <c r="G43" s="3">
-        <v>61600</v>
+        <v>61200</v>
       </c>
       <c r="H43" s="3">
         <v>4100</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7200</v>
+        <v>6500</v>
       </c>
       <c r="E45" s="3">
-        <v>23500</v>
+        <v>23300</v>
       </c>
       <c r="F45" s="3">
-        <v>14100</v>
+        <v>14000</v>
       </c>
       <c r="G45" s="3">
-        <v>15300</v>
+        <v>15200</v>
       </c>
       <c r="H45" s="3">
-        <v>22600</v>
+        <v>22400</v>
       </c>
       <c r="I45" s="3">
-        <v>24500</v>
+        <v>24300</v>
       </c>
       <c r="J45" s="3">
-        <v>15800</v>
+        <v>15700</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>324800</v>
+        <v>322800</v>
       </c>
       <c r="E46" s="3">
-        <v>504200</v>
+        <v>501000</v>
       </c>
       <c r="F46" s="3">
-        <v>664800</v>
+        <v>660600</v>
       </c>
       <c r="G46" s="3">
-        <v>742900</v>
+        <v>738300</v>
       </c>
       <c r="H46" s="3">
-        <v>189300</v>
+        <v>188100</v>
       </c>
       <c r="I46" s="3">
-        <v>283200</v>
+        <v>281400</v>
       </c>
       <c r="J46" s="3">
-        <v>96100</v>
+        <v>95600</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2166,10 +2166,10 @@
         <v>4300</v>
       </c>
       <c r="F47" s="3">
-        <v>48900</v>
+        <v>48600</v>
       </c>
       <c r="G47" s="3">
-        <v>92400</v>
+        <v>91900</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2205,16 +2205,16 @@
         <v>11500</v>
       </c>
       <c r="E48" s="3">
-        <v>17200</v>
+        <v>17100</v>
       </c>
       <c r="F48" s="3">
-        <v>22000</v>
+        <v>21900</v>
       </c>
       <c r="G48" s="3">
         <v>5600</v>
       </c>
       <c r="H48" s="3">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="I48" s="3">
         <v>3800</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>16400</v>
+        <v>16300</v>
       </c>
       <c r="E49" s="3">
+        <v>38900</v>
+      </c>
+      <c r="F49" s="3">
+        <v>39000</v>
+      </c>
+      <c r="G49" s="3">
         <v>39100</v>
       </c>
-      <c r="F49" s="3">
-        <v>39200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>39300</v>
-      </c>
       <c r="H49" s="3">
-        <v>43300</v>
+        <v>43000</v>
       </c>
       <c r="I49" s="3">
-        <v>43300</v>
+        <v>43000</v>
       </c>
       <c r="J49" s="3">
-        <v>43300</v>
+        <v>43000</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2370,7 +2370,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8800</v>
+        <v>8700</v>
       </c>
       <c r="E52" s="3">
         <v>1500</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>363300</v>
+        <v>361000</v>
       </c>
       <c r="E54" s="3">
-        <v>566300</v>
+        <v>562800</v>
       </c>
       <c r="F54" s="3">
-        <v>778700</v>
+        <v>773900</v>
       </c>
       <c r="G54" s="3">
-        <v>880500</v>
+        <v>875100</v>
       </c>
       <c r="H54" s="3">
-        <v>241600</v>
+        <v>240100</v>
       </c>
       <c r="I54" s="3">
-        <v>330300</v>
+        <v>328300</v>
       </c>
       <c r="J54" s="3">
-        <v>142500</v>
+        <v>141700</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2531,14 +2531,14 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>49700</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F57" s="3">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2574,7 +2574,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4200</v>
+        <v>4100</v>
       </c>
       <c r="E58" s="3">
         <v>2600</v>
@@ -2586,13 +2586,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="I58" s="3">
         <v>11100</v>
       </c>
       <c r="J58" s="3">
-        <v>13800</v>
+        <v>13700</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3300</v>
+        <v>52800</v>
       </c>
       <c r="E59" s="3">
-        <v>102800</v>
+        <v>102100</v>
       </c>
       <c r="F59" s="3">
-        <v>78800</v>
+        <v>78300</v>
       </c>
       <c r="G59" s="3">
-        <v>80100</v>
+        <v>79600</v>
       </c>
       <c r="H59" s="3">
-        <v>74900</v>
+        <v>74400</v>
       </c>
       <c r="I59" s="3">
-        <v>37000</v>
+        <v>36800</v>
       </c>
       <c r="J59" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>57300</v>
+        <v>56900</v>
       </c>
       <c r="E60" s="3">
-        <v>105400</v>
+        <v>104700</v>
       </c>
       <c r="F60" s="3">
-        <v>86700</v>
+        <v>86200</v>
       </c>
       <c r="G60" s="3">
-        <v>80100</v>
+        <v>79600</v>
       </c>
       <c r="H60" s="3">
-        <v>81800</v>
+        <v>81300</v>
       </c>
       <c r="I60" s="3">
-        <v>48100</v>
+        <v>47800</v>
       </c>
       <c r="J60" s="3">
-        <v>27100</v>
+        <v>27000</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2700,7 +2700,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>9500</v>
+        <v>9400</v>
       </c>
       <c r="I61" s="3">
         <v>9300</v>
@@ -2742,16 +2742,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>67100</v>
+        <v>58600</v>
       </c>
       <c r="E62" s="3">
-        <v>56400</v>
+        <v>56000</v>
       </c>
       <c r="F62" s="3">
-        <v>58100</v>
+        <v>57700</v>
       </c>
       <c r="G62" s="3">
-        <v>18100</v>
+        <v>18000</v>
       </c>
       <c r="H62" s="3">
         <v>1600</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>124400</v>
+        <v>123600</v>
       </c>
       <c r="E66" s="3">
-        <v>161800</v>
+        <v>160800</v>
       </c>
       <c r="F66" s="3">
-        <v>144800</v>
+        <v>143900</v>
       </c>
       <c r="G66" s="3">
-        <v>98200</v>
+        <v>97600</v>
       </c>
       <c r="H66" s="3">
-        <v>92900</v>
+        <v>92300</v>
       </c>
       <c r="I66" s="3">
-        <v>57800</v>
+        <v>57400</v>
       </c>
       <c r="J66" s="3">
-        <v>85500</v>
+        <v>84900</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -3066,13 +3066,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>431500</v>
+        <v>428900</v>
       </c>
       <c r="I70" s="3">
-        <v>405300</v>
+        <v>402800</v>
       </c>
       <c r="J70" s="3">
-        <v>98700</v>
+        <v>98100</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1157700</v>
+        <v>-1150600</v>
       </c>
       <c r="E72" s="3">
-        <v>-954000</v>
+        <v>-948100</v>
       </c>
       <c r="F72" s="3">
-        <v>-605400</v>
+        <v>-601700</v>
       </c>
       <c r="G72" s="3">
-        <v>-281300</v>
+        <v>-279500</v>
       </c>
       <c r="H72" s="3">
-        <v>-346700</v>
+        <v>-344600</v>
       </c>
       <c r="I72" s="3">
-        <v>-141000</v>
+        <v>-140200</v>
       </c>
       <c r="J72" s="3">
-        <v>-49700</v>
+        <v>-49400</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>238900</v>
+        <v>237400</v>
       </c>
       <c r="E76" s="3">
-        <v>404500</v>
+        <v>402000</v>
       </c>
       <c r="F76" s="3">
-        <v>633900</v>
+        <v>629900</v>
       </c>
       <c r="G76" s="3">
-        <v>782300</v>
+        <v>777400</v>
       </c>
       <c r="H76" s="3">
-        <v>-282800</v>
+        <v>-281100</v>
       </c>
       <c r="I76" s="3">
-        <v>-132800</v>
+        <v>-132000</v>
       </c>
       <c r="J76" s="3">
-        <v>-41600</v>
+        <v>-41400</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3436,26 +3436,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-202500</v>
       </c>
       <c r="E81" s="3">
-        <v>-348600</v>
+        <v>-346400</v>
       </c>
       <c r="F81" s="3">
-        <v>-324100</v>
+        <v>-322100</v>
       </c>
       <c r="G81" s="3">
-        <v>65500</v>
+        <v>65100</v>
       </c>
       <c r="H81" s="3">
-        <v>-206400</v>
+        <v>-205200</v>
       </c>
       <c r="I81" s="3">
-        <v>-56000</v>
+        <v>-55700</v>
       </c>
       <c r="J81" s="3">
-        <v>-41500</v>
+        <v>-41200</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3496,8 +3496,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>3400</v>
       </c>
       <c r="E83" s="3">
         <v>3600</v>
@@ -3748,26 +3748,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-180300</v>
       </c>
       <c r="E89" s="3">
-        <v>-153300</v>
+        <v>-152400</v>
       </c>
       <c r="F89" s="3">
-        <v>-135300</v>
+        <v>-134400</v>
       </c>
       <c r="G89" s="3">
-        <v>60300</v>
+        <v>59900</v>
       </c>
       <c r="H89" s="3">
-        <v>-120700</v>
+        <v>-119900</v>
       </c>
       <c r="I89" s="3">
-        <v>-39000</v>
+        <v>-38800</v>
       </c>
       <c r="J89" s="3">
-        <v>-35100</v>
+        <v>-34800</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3808,14 +3808,14 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-1600</v>
       </c>
       <c r="E91" s="3">
-        <v>-6400</v>
+        <v>-6300</v>
       </c>
       <c r="F91" s="3">
-        <v>-4200</v>
+        <v>-4100</v>
       </c>
       <c r="G91" s="3">
         <v>-1100</v>
@@ -3934,26 +3934,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>14200</v>
       </c>
       <c r="E94" s="3">
-        <v>63700</v>
+        <v>63300</v>
       </c>
       <c r="F94" s="3">
-        <v>-101100</v>
+        <v>-100500</v>
       </c>
       <c r="G94" s="3">
-        <v>-28100</v>
+        <v>-27900</v>
       </c>
       <c r="H94" s="3">
-        <v>29500</v>
+        <v>29400</v>
       </c>
       <c r="I94" s="3">
         <v>1300</v>
       </c>
       <c r="J94" s="3">
-        <v>-21900</v>
+        <v>-21800</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -4162,26 +4162,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>1000</v>
       </c>
       <c r="E100" s="3">
         <v>5900</v>
       </c>
       <c r="F100" s="3">
-        <v>82600</v>
+        <v>82100</v>
       </c>
       <c r="G100" s="3">
-        <v>478300</v>
+        <v>475300</v>
       </c>
       <c r="H100" s="3">
-        <v>21200</v>
+        <v>21100</v>
       </c>
       <c r="I100" s="3">
-        <v>205700</v>
+        <v>204400</v>
       </c>
       <c r="J100" s="3">
-        <v>105500</v>
+        <v>104800</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -4204,17 +4204,17 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>11700</v>
       </c>
       <c r="E101" s="3">
-        <v>54100</v>
+        <v>53800</v>
       </c>
       <c r="F101" s="3">
-        <v>-17900</v>
+        <v>-17800</v>
       </c>
       <c r="G101" s="3">
-        <v>-14800</v>
+        <v>-14700</v>
       </c>
       <c r="H101" s="3">
         <v>2100</v>
@@ -4246,26 +4246,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-153400</v>
       </c>
       <c r="E102" s="3">
-        <v>-29600</v>
+        <v>-29400</v>
       </c>
       <c r="F102" s="3">
-        <v>-171700</v>
+        <v>-170600</v>
       </c>
       <c r="G102" s="3">
-        <v>495700</v>
+        <v>492600</v>
       </c>
       <c r="H102" s="3">
-        <v>-67800</v>
+        <v>-67400</v>
       </c>
       <c r="I102" s="3">
-        <v>176300</v>
+        <v>175200</v>
       </c>
       <c r="J102" s="3">
-        <v>48500</v>
+        <v>48200</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/IMAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IMAB_YR_FIN.xlsx
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>3800</v>
+        <v>27600</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="3">
-        <v>12200</v>
+        <v>88000</v>
       </c>
       <c r="G8" s="3">
-        <v>213100</v>
+        <v>1542700</v>
       </c>
       <c r="H8" s="3">
-        <v>4100</v>
+        <v>30000</v>
       </c>
       <c r="I8" s="3">
-        <v>7400</v>
+        <v>53800</v>
       </c>
       <c r="J8" s="3">
-        <v>1600</v>
+        <v>11600</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -769,10 +769,10 @@
         <v>3</v>
       </c>
       <c r="E9" s="3">
-        <v>3800</v>
+        <v>27200</v>
       </c>
       <c r="F9" s="3">
-        <v>6400</v>
+        <v>46400</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -814,7 +814,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="3">
-        <v>5700</v>
+        <v>41600</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -868,25 +868,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>112000</v>
+        <v>810600</v>
       </c>
       <c r="E12" s="3">
-        <v>125000</v>
+        <v>904900</v>
       </c>
       <c r="F12" s="3">
-        <v>167600</v>
+        <v>1213000</v>
       </c>
       <c r="G12" s="3">
-        <v>136000</v>
+        <v>984700</v>
       </c>
       <c r="H12" s="3">
-        <v>116100</v>
+        <v>840400</v>
       </c>
       <c r="I12" s="3">
-        <v>58900</v>
+        <v>426000</v>
       </c>
       <c r="J12" s="3">
-        <v>36900</v>
+        <v>267100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -952,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>23600</v>
+        <v>170500</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -961,10 +961,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>-56300</v>
+        <v>-407600</v>
       </c>
       <c r="H14" s="3">
-        <v>3200</v>
+        <v>23000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>198100</v>
+        <v>1434100</v>
       </c>
       <c r="E17" s="3">
-        <v>241500</v>
+        <v>1747900</v>
       </c>
       <c r="F17" s="3">
-        <v>298300</v>
+        <v>2159300</v>
       </c>
       <c r="G17" s="3">
-        <v>135300</v>
+        <v>979500</v>
       </c>
       <c r="H17" s="3">
-        <v>209700</v>
+        <v>1518000</v>
       </c>
       <c r="I17" s="3">
-        <v>68000</v>
+        <v>492400</v>
       </c>
       <c r="J17" s="3">
-        <v>40400</v>
+        <v>292500</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-194300</v>
+        <v>-1406500</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="3">
-        <v>-286200</v>
+        <v>-2071300</v>
       </c>
       <c r="G18" s="3">
-        <v>77800</v>
+        <v>563200</v>
       </c>
       <c r="H18" s="3">
-        <v>-205600</v>
+        <v>-1488000</v>
       </c>
       <c r="I18" s="3">
-        <v>-60600</v>
+        <v>-438600</v>
       </c>
       <c r="J18" s="3">
-        <v>-38800</v>
+        <v>-281000</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-8100</v>
+        <v>-58500</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>-36400</v>
+        <v>-263400</v>
       </c>
       <c r="G20" s="3">
-        <v>-10900</v>
+        <v>-79100</v>
       </c>
       <c r="H20" s="3">
-        <v>5400</v>
+        <v>39000</v>
       </c>
       <c r="I20" s="3">
-        <v>6800</v>
+        <v>49200</v>
       </c>
       <c r="J20" s="3">
-        <v>-1600</v>
+        <v>-11600</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-199000</v>
+        <v>-1440200</v>
       </c>
       <c r="E21" s="3">
-        <v>-342700</v>
+        <v>-2480500</v>
       </c>
       <c r="F21" s="3">
-        <v>-320600</v>
+        <v>-2320100</v>
       </c>
       <c r="G21" s="3">
-        <v>68900</v>
+        <v>498400</v>
       </c>
       <c r="H21" s="3">
-        <v>-198800</v>
+        <v>-1439100</v>
       </c>
       <c r="I21" s="3">
-        <v>-52900</v>
+        <v>-382700</v>
       </c>
       <c r="J21" s="3">
-        <v>-40200</v>
+        <v>-291000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1237,7 +1237,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1246,16 +1246,16 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H22" s="3">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="I22" s="3">
-        <v>1600</v>
+        <v>11700</v>
       </c>
       <c r="J22" s="3">
-        <v>800</v>
+        <v>5600</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-202500</v>
+        <v>-1465700</v>
       </c>
       <c r="E23" s="3">
-        <v>-346300</v>
+        <v>-2506600</v>
       </c>
       <c r="F23" s="3">
-        <v>-322600</v>
+        <v>-2334700</v>
       </c>
       <c r="G23" s="3">
-        <v>66800</v>
+        <v>483100</v>
       </c>
       <c r="H23" s="3">
-        <v>-200600</v>
+        <v>-1452000</v>
       </c>
       <c r="I23" s="3">
-        <v>-55400</v>
+        <v>-401100</v>
       </c>
       <c r="J23" s="3">
-        <v>-41200</v>
+        <v>-298200</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1324,19 +1324,19 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F24" s="3">
-        <v>-400</v>
+        <v>-3200</v>
       </c>
       <c r="G24" s="3">
+        <v>12200</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>1700</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-202500</v>
+        <v>-1465700</v>
       </c>
       <c r="E26" s="3">
-        <v>-346400</v>
+        <v>-2507300</v>
       </c>
       <c r="F26" s="3">
-        <v>-322100</v>
+        <v>-2331500</v>
       </c>
       <c r="G26" s="3">
-        <v>65100</v>
+        <v>470900</v>
       </c>
       <c r="H26" s="3">
-        <v>-200600</v>
+        <v>-1452000</v>
       </c>
       <c r="I26" s="3">
-        <v>-55700</v>
+        <v>-402800</v>
       </c>
       <c r="J26" s="3">
-        <v>-41200</v>
+        <v>-298200</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-202500</v>
+        <v>-1465700</v>
       </c>
       <c r="E27" s="3">
-        <v>-346400</v>
+        <v>-2507300</v>
       </c>
       <c r="F27" s="3">
-        <v>-322100</v>
+        <v>-2331500</v>
       </c>
       <c r="G27" s="3">
-        <v>65100</v>
+        <v>470900</v>
       </c>
       <c r="H27" s="3">
-        <v>-205200</v>
+        <v>-1485000</v>
       </c>
       <c r="I27" s="3">
-        <v>-55700</v>
+        <v>-402800</v>
       </c>
       <c r="J27" s="3">
-        <v>-41200</v>
+        <v>-298200</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>8100</v>
+        <v>58500</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>36400</v>
+        <v>263400</v>
       </c>
       <c r="G32" s="3">
-        <v>10900</v>
+        <v>79100</v>
       </c>
       <c r="H32" s="3">
-        <v>-5400</v>
+        <v>-39000</v>
       </c>
       <c r="I32" s="3">
-        <v>-6800</v>
+        <v>-49200</v>
       </c>
       <c r="J32" s="3">
-        <v>1600</v>
+        <v>11600</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-202500</v>
+        <v>-1465700</v>
       </c>
       <c r="E33" s="3">
-        <v>-346400</v>
+        <v>-2507300</v>
       </c>
       <c r="F33" s="3">
-        <v>-322100</v>
+        <v>-2331500</v>
       </c>
       <c r="G33" s="3">
-        <v>65100</v>
+        <v>470900</v>
       </c>
       <c r="H33" s="3">
-        <v>-205200</v>
+        <v>-1485000</v>
       </c>
       <c r="I33" s="3">
-        <v>-55700</v>
+        <v>-402800</v>
       </c>
       <c r="J33" s="3">
-        <v>-41200</v>
+        <v>-298200</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-202500</v>
+        <v>-1465700</v>
       </c>
       <c r="E35" s="3">
-        <v>-346400</v>
+        <v>-2507300</v>
       </c>
       <c r="F35" s="3">
-        <v>-322100</v>
+        <v>-2331500</v>
       </c>
       <c r="G35" s="3">
-        <v>65100</v>
+        <v>470900</v>
       </c>
       <c r="H35" s="3">
-        <v>-205200</v>
+        <v>-1485000</v>
       </c>
       <c r="I35" s="3">
-        <v>-55700</v>
+        <v>-402800</v>
       </c>
       <c r="J35" s="3">
-        <v>-41200</v>
+        <v>-298200</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>295900</v>
+        <v>2141400</v>
       </c>
       <c r="E41" s="3">
-        <v>444000</v>
+        <v>3214000</v>
       </c>
       <c r="F41" s="3">
-        <v>486800</v>
+        <v>3523600</v>
       </c>
       <c r="G41" s="3">
-        <v>657500</v>
+        <v>4758800</v>
       </c>
       <c r="H41" s="3">
-        <v>157200</v>
+        <v>1137500</v>
       </c>
       <c r="I41" s="3">
-        <v>219400</v>
+        <v>1588300</v>
       </c>
       <c r="J41" s="3">
-        <v>42500</v>
+        <v>307900</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>19800</v>
+        <v>143200</v>
       </c>
       <c r="E42" s="3">
-        <v>32500</v>
+        <v>235400</v>
       </c>
       <c r="F42" s="3">
-        <v>104100</v>
+        <v>753200</v>
       </c>
       <c r="G42" s="3">
-        <v>4400</v>
+        <v>31500</v>
       </c>
       <c r="H42" s="3">
-        <v>4400</v>
+        <v>32000</v>
       </c>
       <c r="I42" s="3">
-        <v>29800</v>
+        <v>215600</v>
       </c>
       <c r="J42" s="3">
-        <v>36800</v>
+        <v>266200</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>600</v>
+        <v>4700</v>
       </c>
       <c r="E43" s="3">
-        <v>1100</v>
+        <v>8200</v>
       </c>
       <c r="F43" s="3">
-        <v>52000</v>
+        <v>376400</v>
       </c>
       <c r="G43" s="3">
-        <v>61200</v>
+        <v>443000</v>
       </c>
       <c r="H43" s="3">
-        <v>4100</v>
+        <v>29500</v>
       </c>
       <c r="I43" s="3">
-        <v>7900</v>
+        <v>57100</v>
       </c>
       <c r="J43" s="3">
-        <v>500</v>
+        <v>3800</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>3800</v>
+        <v>27200</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6500</v>
+        <v>47300</v>
       </c>
       <c r="E45" s="3">
-        <v>23300</v>
+        <v>168800</v>
       </c>
       <c r="F45" s="3">
-        <v>14000</v>
+        <v>101200</v>
       </c>
       <c r="G45" s="3">
-        <v>15200</v>
+        <v>110400</v>
       </c>
       <c r="H45" s="3">
-        <v>22400</v>
+        <v>162400</v>
       </c>
       <c r="I45" s="3">
-        <v>24300</v>
+        <v>175900</v>
       </c>
       <c r="J45" s="3">
-        <v>15700</v>
+        <v>113600</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>322800</v>
+        <v>2336700</v>
       </c>
       <c r="E46" s="3">
-        <v>501000</v>
+        <v>3626500</v>
       </c>
       <c r="F46" s="3">
-        <v>660600</v>
+        <v>4781700</v>
       </c>
       <c r="G46" s="3">
-        <v>738300</v>
+        <v>5343700</v>
       </c>
       <c r="H46" s="3">
-        <v>188100</v>
+        <v>1361300</v>
       </c>
       <c r="I46" s="3">
-        <v>281400</v>
+        <v>2036900</v>
       </c>
       <c r="J46" s="3">
-        <v>95600</v>
+        <v>691600</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2160,16 +2160,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1700</v>
+        <v>12100</v>
       </c>
       <c r="E47" s="3">
-        <v>4300</v>
+        <v>30900</v>
       </c>
       <c r="F47" s="3">
-        <v>48600</v>
+        <v>352100</v>
       </c>
       <c r="G47" s="3">
-        <v>91900</v>
+        <v>664800</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11500</v>
+        <v>82900</v>
       </c>
       <c r="E48" s="3">
-        <v>17100</v>
+        <v>124000</v>
       </c>
       <c r="F48" s="3">
-        <v>21900</v>
+        <v>158500</v>
       </c>
       <c r="G48" s="3">
-        <v>5600</v>
+        <v>40300</v>
       </c>
       <c r="H48" s="3">
-        <v>6400</v>
+        <v>46500</v>
       </c>
       <c r="I48" s="3">
-        <v>3800</v>
+        <v>27700</v>
       </c>
       <c r="J48" s="3">
-        <v>3100</v>
+        <v>22300</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>16300</v>
+        <v>118100</v>
       </c>
       <c r="E49" s="3">
-        <v>38900</v>
+        <v>281500</v>
       </c>
       <c r="F49" s="3">
-        <v>39000</v>
+        <v>282200</v>
       </c>
       <c r="G49" s="3">
-        <v>39100</v>
+        <v>283000</v>
       </c>
       <c r="H49" s="3">
-        <v>43000</v>
+        <v>311400</v>
       </c>
       <c r="I49" s="3">
-        <v>43000</v>
+        <v>311400</v>
       </c>
       <c r="J49" s="3">
-        <v>43000</v>
+        <v>311400</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2370,19 +2370,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8700</v>
+        <v>63200</v>
       </c>
       <c r="E52" s="3">
-        <v>1500</v>
+        <v>10900</v>
       </c>
       <c r="F52" s="3">
-        <v>3700</v>
+        <v>26600</v>
       </c>
       <c r="G52" s="3">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="H52" s="3">
-        <v>2500</v>
+        <v>18300</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>361000</v>
+        <v>2613000</v>
       </c>
       <c r="E54" s="3">
-        <v>562800</v>
+        <v>4073700</v>
       </c>
       <c r="F54" s="3">
-        <v>773900</v>
+        <v>5601200</v>
       </c>
       <c r="G54" s="3">
-        <v>875100</v>
+        <v>6333800</v>
       </c>
       <c r="H54" s="3">
-        <v>240100</v>
+        <v>1737600</v>
       </c>
       <c r="I54" s="3">
-        <v>328300</v>
+        <v>2375900</v>
       </c>
       <c r="J54" s="3">
-        <v>141700</v>
+        <v>1025300</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2538,7 +2538,7 @@
         <v>3</v>
       </c>
       <c r="F57" s="3">
-        <v>7900</v>
+        <v>57400</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2574,10 +2574,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4100</v>
+        <v>30000</v>
       </c>
       <c r="E58" s="3">
-        <v>2600</v>
+        <v>19000</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -2586,13 +2586,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>6900</v>
+        <v>50000</v>
       </c>
       <c r="I58" s="3">
-        <v>11100</v>
+        <v>80000</v>
       </c>
       <c r="J58" s="3">
-        <v>13700</v>
+        <v>99000</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>52800</v>
+        <v>381800</v>
       </c>
       <c r="E59" s="3">
-        <v>102100</v>
+        <v>739200</v>
       </c>
       <c r="F59" s="3">
-        <v>78300</v>
+        <v>566600</v>
       </c>
       <c r="G59" s="3">
-        <v>79600</v>
+        <v>576100</v>
       </c>
       <c r="H59" s="3">
-        <v>74400</v>
+        <v>538500</v>
       </c>
       <c r="I59" s="3">
-        <v>36800</v>
+        <v>266200</v>
       </c>
       <c r="J59" s="3">
-        <v>13300</v>
+        <v>96100</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>56900</v>
+        <v>411800</v>
       </c>
       <c r="E60" s="3">
-        <v>104700</v>
+        <v>758200</v>
       </c>
       <c r="F60" s="3">
-        <v>86200</v>
+        <v>624000</v>
       </c>
       <c r="G60" s="3">
-        <v>79600</v>
+        <v>576100</v>
       </c>
       <c r="H60" s="3">
-        <v>81300</v>
+        <v>588500</v>
       </c>
       <c r="I60" s="3">
-        <v>47800</v>
+        <v>346200</v>
       </c>
       <c r="J60" s="3">
-        <v>27000</v>
+        <v>195100</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2700,7 +2700,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8100</v>
+        <v>58900</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>9400</v>
+        <v>68200</v>
       </c>
       <c r="I61" s="3">
-        <v>9300</v>
+        <v>67000</v>
       </c>
       <c r="J61" s="3">
-        <v>15800</v>
+        <v>114000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2742,22 +2742,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>58600</v>
+        <v>424100</v>
       </c>
       <c r="E62" s="3">
-        <v>56000</v>
+        <v>405600</v>
       </c>
       <c r="F62" s="3">
-        <v>57700</v>
+        <v>417600</v>
       </c>
       <c r="G62" s="3">
-        <v>18000</v>
+        <v>130500</v>
       </c>
       <c r="H62" s="3">
-        <v>1600</v>
+        <v>11400</v>
       </c>
       <c r="I62" s="3">
-        <v>300</v>
+        <v>2500</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>123600</v>
+        <v>894800</v>
       </c>
       <c r="E66" s="3">
-        <v>160800</v>
+        <v>1163800</v>
       </c>
       <c r="F66" s="3">
-        <v>143900</v>
+        <v>1041600</v>
       </c>
       <c r="G66" s="3">
-        <v>97600</v>
+        <v>706600</v>
       </c>
       <c r="H66" s="3">
-        <v>92300</v>
+        <v>668100</v>
       </c>
       <c r="I66" s="3">
-        <v>57400</v>
+        <v>415700</v>
       </c>
       <c r="J66" s="3">
-        <v>84900</v>
+        <v>614900</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -3066,13 +3066,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>428900</v>
+        <v>3104200</v>
       </c>
       <c r="I70" s="3">
-        <v>402800</v>
+        <v>2915400</v>
       </c>
       <c r="J70" s="3">
-        <v>98100</v>
+        <v>710300</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1150600</v>
+        <v>-8327800</v>
       </c>
       <c r="E72" s="3">
-        <v>-948100</v>
+        <v>-6862100</v>
       </c>
       <c r="F72" s="3">
-        <v>-601700</v>
+        <v>-4354800</v>
       </c>
       <c r="G72" s="3">
-        <v>-279500</v>
+        <v>-2023300</v>
       </c>
       <c r="H72" s="3">
-        <v>-344600</v>
+        <v>-2494200</v>
       </c>
       <c r="I72" s="3">
-        <v>-140200</v>
+        <v>-1014500</v>
       </c>
       <c r="J72" s="3">
-        <v>-49400</v>
+        <v>-357900</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>237400</v>
+        <v>1718200</v>
       </c>
       <c r="E76" s="3">
-        <v>402000</v>
+        <v>2909900</v>
       </c>
       <c r="F76" s="3">
-        <v>629900</v>
+        <v>4559600</v>
       </c>
       <c r="G76" s="3">
-        <v>777400</v>
+        <v>5627100</v>
       </c>
       <c r="H76" s="3">
-        <v>-281100</v>
+        <v>-2034700</v>
       </c>
       <c r="I76" s="3">
-        <v>-132000</v>
+        <v>-955100</v>
       </c>
       <c r="J76" s="3">
-        <v>-41400</v>
+        <v>-299800</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-202500</v>
+        <v>-1465700</v>
       </c>
       <c r="E81" s="3">
-        <v>-346400</v>
+        <v>-2507300</v>
       </c>
       <c r="F81" s="3">
-        <v>-322100</v>
+        <v>-2331500</v>
       </c>
       <c r="G81" s="3">
-        <v>65100</v>
+        <v>470900</v>
       </c>
       <c r="H81" s="3">
-        <v>-205200</v>
+        <v>-1485000</v>
       </c>
       <c r="I81" s="3">
-        <v>-55700</v>
+        <v>-402800</v>
       </c>
       <c r="J81" s="3">
-        <v>-41200</v>
+        <v>-298200</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3400</v>
+        <v>24700</v>
       </c>
       <c r="E83" s="3">
-        <v>3600</v>
+        <v>26100</v>
       </c>
       <c r="F83" s="3">
-        <v>2000</v>
+        <v>14600</v>
       </c>
       <c r="G83" s="3">
-        <v>2000</v>
+        <v>14300</v>
       </c>
       <c r="H83" s="3">
-        <v>1400</v>
+        <v>9800</v>
       </c>
       <c r="I83" s="3">
-        <v>900</v>
+        <v>6700</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-180300</v>
+        <v>-1305000</v>
       </c>
       <c r="E89" s="3">
-        <v>-152400</v>
+        <v>-1102800</v>
       </c>
       <c r="F89" s="3">
-        <v>-134400</v>
+        <v>-973100</v>
       </c>
       <c r="G89" s="3">
-        <v>59900</v>
+        <v>433600</v>
       </c>
       <c r="H89" s="3">
-        <v>-119900</v>
+        <v>-868000</v>
       </c>
       <c r="I89" s="3">
-        <v>-38800</v>
+        <v>-280700</v>
       </c>
       <c r="J89" s="3">
-        <v>-34800</v>
+        <v>-252200</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1600</v>
+        <v>-11400</v>
       </c>
       <c r="E91" s="3">
-        <v>-6300</v>
+        <v>-45800</v>
       </c>
       <c r="F91" s="3">
-        <v>-4100</v>
+        <v>-29900</v>
       </c>
       <c r="G91" s="3">
-        <v>-1100</v>
+        <v>-8000</v>
       </c>
       <c r="H91" s="3">
-        <v>-1700</v>
+        <v>-12200</v>
       </c>
       <c r="I91" s="3">
-        <v>-2000</v>
+        <v>-14400</v>
       </c>
       <c r="J91" s="3">
-        <v>-2800</v>
+        <v>-20300</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>14200</v>
+        <v>102500</v>
       </c>
       <c r="E94" s="3">
-        <v>63300</v>
+        <v>458400</v>
       </c>
       <c r="F94" s="3">
-        <v>-100500</v>
+        <v>-727200</v>
       </c>
       <c r="G94" s="3">
-        <v>-27900</v>
+        <v>-201900</v>
       </c>
       <c r="H94" s="3">
-        <v>29400</v>
+        <v>212500</v>
       </c>
       <c r="I94" s="3">
-        <v>1300</v>
+        <v>9500</v>
       </c>
       <c r="J94" s="3">
-        <v>-21800</v>
+        <v>-157700</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="E100" s="3">
-        <v>5900</v>
+        <v>42400</v>
       </c>
       <c r="F100" s="3">
-        <v>82100</v>
+        <v>593900</v>
       </c>
       <c r="G100" s="3">
-        <v>475300</v>
+        <v>3440500</v>
       </c>
       <c r="H100" s="3">
-        <v>21100</v>
+        <v>152700</v>
       </c>
       <c r="I100" s="3">
-        <v>204400</v>
+        <v>1479700</v>
       </c>
       <c r="J100" s="3">
-        <v>104800</v>
+        <v>758600</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -4205,25 +4205,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>11700</v>
+        <v>84500</v>
       </c>
       <c r="E101" s="3">
-        <v>53800</v>
+        <v>389200</v>
       </c>
       <c r="F101" s="3">
-        <v>-17800</v>
+        <v>-128800</v>
       </c>
       <c r="G101" s="3">
-        <v>-14700</v>
+        <v>-106600</v>
       </c>
       <c r="H101" s="3">
-        <v>2100</v>
+        <v>15200</v>
       </c>
       <c r="I101" s="3">
-        <v>8300</v>
+        <v>59800</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-153400</v>
+        <v>-1110400</v>
       </c>
       <c r="E102" s="3">
-        <v>-29400</v>
+        <v>-212900</v>
       </c>
       <c r="F102" s="3">
-        <v>-170600</v>
+        <v>-1235100</v>
       </c>
       <c r="G102" s="3">
-        <v>492600</v>
+        <v>3565500</v>
       </c>
       <c r="H102" s="3">
-        <v>-67400</v>
+        <v>-487600</v>
       </c>
       <c r="I102" s="3">
-        <v>175200</v>
+        <v>1268200</v>
       </c>
       <c r="J102" s="3">
-        <v>48200</v>
+        <v>348600</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/IMAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IMAB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -724,25 +724,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>27600</v>
+        <v>3900</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="3">
-        <v>88000</v>
+        <v>13900</v>
       </c>
       <c r="G8" s="3">
-        <v>1542700</v>
+        <v>236300</v>
       </c>
       <c r="H8" s="3">
-        <v>30000</v>
+        <v>4300</v>
       </c>
       <c r="I8" s="3">
-        <v>53800</v>
+        <v>7800</v>
       </c>
       <c r="J8" s="3">
-        <v>11600</v>
+        <v>1800</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -769,10 +769,10 @@
         <v>3</v>
       </c>
       <c r="E9" s="3">
-        <v>27200</v>
+        <v>3900</v>
       </c>
       <c r="F9" s="3">
-        <v>46400</v>
+        <v>7300</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -807,26 +807,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-36100</v>
       </c>
       <c r="F10" s="3">
-        <v>41600</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>6500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>236300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -868,25 +868,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>810600</v>
+        <v>114300</v>
       </c>
       <c r="E12" s="3">
-        <v>904900</v>
+        <v>131200</v>
       </c>
       <c r="F12" s="3">
-        <v>1213000</v>
+        <v>190900</v>
       </c>
       <c r="G12" s="3">
-        <v>984700</v>
+        <v>150800</v>
       </c>
       <c r="H12" s="3">
-        <v>840400</v>
+        <v>120700</v>
       </c>
       <c r="I12" s="3">
-        <v>426000</v>
+        <v>61900</v>
       </c>
       <c r="J12" s="3">
-        <v>267100</v>
+        <v>41000</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -952,22 +952,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>170500</v>
+        <v>20300</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-4800</v>
       </c>
       <c r="G14" s="3">
-        <v>-407600</v>
+        <v>-64200</v>
       </c>
       <c r="H14" s="3">
-        <v>23000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+        <v>3200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>3900</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1051,25 +1051,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1434100</v>
+        <v>178200</v>
       </c>
       <c r="E17" s="3">
-        <v>1747900</v>
+        <v>253400</v>
       </c>
       <c r="F17" s="3">
-        <v>2159300</v>
+        <v>339900</v>
       </c>
       <c r="G17" s="3">
-        <v>979500</v>
+        <v>212500</v>
       </c>
       <c r="H17" s="3">
-        <v>1518000</v>
+        <v>214700</v>
       </c>
       <c r="I17" s="3">
-        <v>492400</v>
+        <v>71600</v>
       </c>
       <c r="J17" s="3">
-        <v>292500</v>
+        <v>45000</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1093,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1406500</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
+        <v>-174300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-285500</v>
       </c>
       <c r="F18" s="3">
-        <v>-2071300</v>
+        <v>-326100</v>
       </c>
       <c r="G18" s="3">
-        <v>563200</v>
+        <v>23800</v>
       </c>
       <c r="H18" s="3">
-        <v>-1488000</v>
+        <v>-210400</v>
       </c>
       <c r="I18" s="3">
-        <v>-438600</v>
+        <v>-63800</v>
       </c>
       <c r="J18" s="3">
-        <v>-281000</v>
+        <v>-43200</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-58500</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+        <v>19300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>79800</v>
       </c>
       <c r="F20" s="3">
-        <v>-263400</v>
+        <v>49600</v>
       </c>
       <c r="G20" s="3">
-        <v>-79100</v>
+        <v>17600</v>
       </c>
       <c r="H20" s="3">
-        <v>39000</v>
+        <v>-1100</v>
       </c>
       <c r="I20" s="3">
-        <v>49200</v>
+        <v>-8400</v>
       </c>
       <c r="J20" s="3">
-        <v>-11600</v>
+        <v>2800</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1440200</v>
+        <v>-190200</v>
       </c>
       <c r="E21" s="3">
-        <v>-2480500</v>
+        <v>-361700</v>
       </c>
       <c r="F21" s="3">
-        <v>-2320100</v>
+        <v>-373500</v>
       </c>
       <c r="G21" s="3">
-        <v>498400</v>
+        <v>8200</v>
       </c>
       <c r="H21" s="3">
-        <v>-1439100</v>
+        <v>-207900</v>
       </c>
       <c r="I21" s="3">
-        <v>-382700</v>
+        <v>-54400</v>
       </c>
       <c r="J21" s="3">
-        <v>-291000</v>
+        <v>-45700</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1237,25 +1237,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="I22" s="3">
-        <v>11700</v>
+        <v>1700</v>
       </c>
       <c r="J22" s="3">
-        <v>5600</v>
+        <v>900</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1279,25 +1279,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1465700</v>
+        <v>-206700</v>
       </c>
       <c r="E23" s="3">
-        <v>-2506600</v>
+        <v>-363400</v>
       </c>
       <c r="F23" s="3">
-        <v>-2334700</v>
+        <v>-367500</v>
       </c>
       <c r="G23" s="3">
-        <v>483100</v>
+        <v>74000</v>
       </c>
       <c r="H23" s="3">
-        <v>-1452000</v>
+        <v>-208500</v>
       </c>
       <c r="I23" s="3">
-        <v>-401100</v>
+        <v>-58300</v>
       </c>
       <c r="J23" s="3">
-        <v>-298200</v>
+        <v>-45800</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1320,26 +1320,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>-3200</v>
+        <v>-500</v>
       </c>
       <c r="G24" s="3">
-        <v>12200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
+        <v>1900</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I24" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1405,25 +1405,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1465700</v>
+        <v>-206700</v>
       </c>
       <c r="E26" s="3">
-        <v>-2507300</v>
+        <v>-363500</v>
       </c>
       <c r="F26" s="3">
-        <v>-2331500</v>
+        <v>-367000</v>
       </c>
       <c r="G26" s="3">
-        <v>470900</v>
+        <v>72100</v>
       </c>
       <c r="H26" s="3">
-        <v>-1452000</v>
+        <v>-208500</v>
       </c>
       <c r="I26" s="3">
-        <v>-402800</v>
+        <v>-58600</v>
       </c>
       <c r="J26" s="3">
-        <v>-298200</v>
+        <v>-45800</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1447,25 +1447,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1465700</v>
+        <v>-206700</v>
       </c>
       <c r="E27" s="3">
-        <v>-2507300</v>
+        <v>-363500</v>
       </c>
       <c r="F27" s="3">
-        <v>-2331500</v>
+        <v>-367000</v>
       </c>
       <c r="G27" s="3">
-        <v>470900</v>
+        <v>72100</v>
       </c>
       <c r="H27" s="3">
-        <v>-1485000</v>
+        <v>-213300</v>
       </c>
       <c r="I27" s="3">
-        <v>-402800</v>
+        <v>-58600</v>
       </c>
       <c r="J27" s="3">
-        <v>-298200</v>
+        <v>-45800</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>58500</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+        <v>-19300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-79800</v>
       </c>
       <c r="F32" s="3">
-        <v>263400</v>
+        <v>-49600</v>
       </c>
       <c r="G32" s="3">
-        <v>79100</v>
+        <v>-17600</v>
       </c>
       <c r="H32" s="3">
-        <v>-39000</v>
+        <v>1100</v>
       </c>
       <c r="I32" s="3">
-        <v>-49200</v>
+        <v>8400</v>
       </c>
       <c r="J32" s="3">
-        <v>11600</v>
+        <v>-2800</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1699,25 +1699,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1465700</v>
+        <v>-206700</v>
       </c>
       <c r="E33" s="3">
-        <v>-2507300</v>
+        <v>-363500</v>
       </c>
       <c r="F33" s="3">
-        <v>-2331500</v>
+        <v>-367000</v>
       </c>
       <c r="G33" s="3">
-        <v>470900</v>
+        <v>72100</v>
       </c>
       <c r="H33" s="3">
-        <v>-1485000</v>
+        <v>-208500</v>
       </c>
       <c r="I33" s="3">
-        <v>-402800</v>
+        <v>-58600</v>
       </c>
       <c r="J33" s="3">
-        <v>-298200</v>
+        <v>-45800</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1783,25 +1783,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1465700</v>
+        <v>-206700</v>
       </c>
       <c r="E35" s="3">
-        <v>-2507300</v>
+        <v>-363500</v>
       </c>
       <c r="F35" s="3">
-        <v>-2331500</v>
+        <v>-367000</v>
       </c>
       <c r="G35" s="3">
-        <v>470900</v>
+        <v>72100</v>
       </c>
       <c r="H35" s="3">
-        <v>-1485000</v>
+        <v>-208500</v>
       </c>
       <c r="I35" s="3">
-        <v>-402800</v>
+        <v>-58600</v>
       </c>
       <c r="J35" s="3">
-        <v>-298200</v>
+        <v>-45800</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1908,25 +1908,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2141400</v>
+        <v>302000</v>
       </c>
       <c r="E41" s="3">
-        <v>3214000</v>
+        <v>466000</v>
       </c>
       <c r="F41" s="3">
-        <v>3523600</v>
+        <v>554700</v>
       </c>
       <c r="G41" s="3">
-        <v>4758800</v>
+        <v>728900</v>
       </c>
       <c r="H41" s="3">
-        <v>1137500</v>
+        <v>163400</v>
       </c>
       <c r="I41" s="3">
-        <v>1588300</v>
+        <v>230900</v>
       </c>
       <c r="J41" s="3">
-        <v>307900</v>
+        <v>47300</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1950,25 +1950,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>143200</v>
+        <v>20900</v>
       </c>
       <c r="E42" s="3">
-        <v>235400</v>
+        <v>34800</v>
       </c>
       <c r="F42" s="3">
-        <v>753200</v>
+        <v>118600</v>
       </c>
       <c r="G42" s="3">
-        <v>31500</v>
+        <v>4800</v>
       </c>
       <c r="H42" s="3">
-        <v>32000</v>
+        <v>4600</v>
       </c>
       <c r="I42" s="3">
-        <v>215600</v>
+        <v>31300</v>
       </c>
       <c r="J42" s="3">
-        <v>266200</v>
+        <v>40900</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1992,25 +1992,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4700</v>
+        <v>2500</v>
       </c>
       <c r="E43" s="3">
-        <v>8200</v>
+        <v>4800</v>
       </c>
       <c r="F43" s="3">
-        <v>376400</v>
+        <v>61200</v>
       </c>
       <c r="G43" s="3">
-        <v>443000</v>
+        <v>71400</v>
       </c>
       <c r="H43" s="3">
-        <v>29500</v>
+        <v>8000</v>
       </c>
       <c r="I43" s="3">
-        <v>57100</v>
+        <v>9300</v>
       </c>
       <c r="J43" s="3">
-        <v>3800</v>
+        <v>600</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2036,11 +2036,11 @@
       <c r="D44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F44" s="3">
-        <v>27200</v>
+        <v>4300</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>47300</v>
+        <v>1300</v>
       </c>
       <c r="E45" s="3">
-        <v>168800</v>
+        <v>4800</v>
       </c>
       <c r="F45" s="3">
-        <v>101200</v>
+        <v>12600</v>
       </c>
       <c r="G45" s="3">
-        <v>110400</v>
+        <v>13000</v>
       </c>
       <c r="H45" s="3">
-        <v>162400</v>
+        <v>11400</v>
       </c>
       <c r="I45" s="3">
-        <v>175900</v>
+        <v>10600</v>
       </c>
       <c r="J45" s="3">
-        <v>113600</v>
+        <v>900</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2118,25 +2118,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2336700</v>
+        <v>329500</v>
       </c>
       <c r="E46" s="3">
-        <v>3626500</v>
+        <v>525800</v>
       </c>
       <c r="F46" s="3">
-        <v>4781700</v>
+        <v>752700</v>
       </c>
       <c r="G46" s="3">
-        <v>5343700</v>
+        <v>818500</v>
       </c>
       <c r="H46" s="3">
-        <v>1361300</v>
+        <v>195500</v>
       </c>
       <c r="I46" s="3">
-        <v>2036900</v>
+        <v>296200</v>
       </c>
       <c r="J46" s="3">
-        <v>691600</v>
+        <v>106300</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2160,16 +2160,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>12100</v>
+        <v>1700</v>
       </c>
       <c r="E47" s="3">
-        <v>30900</v>
+        <v>4500</v>
       </c>
       <c r="F47" s="3">
-        <v>352100</v>
+        <v>55400</v>
       </c>
       <c r="G47" s="3">
-        <v>664800</v>
+        <v>101800</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2202,25 +2202,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>82900</v>
+        <v>11700</v>
       </c>
       <c r="E48" s="3">
-        <v>124000</v>
+        <v>18000</v>
       </c>
       <c r="F48" s="3">
-        <v>158500</v>
+        <v>24900</v>
       </c>
       <c r="G48" s="3">
-        <v>40300</v>
+        <v>6200</v>
       </c>
       <c r="H48" s="3">
-        <v>46500</v>
+        <v>6700</v>
       </c>
       <c r="I48" s="3">
-        <v>27700</v>
+        <v>4000</v>
       </c>
       <c r="J48" s="3">
-        <v>22300</v>
+        <v>3400</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2244,25 +2244,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>118100</v>
+        <v>16700</v>
       </c>
       <c r="E49" s="3">
-        <v>281500</v>
+        <v>40800</v>
       </c>
       <c r="F49" s="3">
-        <v>282200</v>
+        <v>44400</v>
       </c>
       <c r="G49" s="3">
-        <v>283000</v>
+        <v>43400</v>
       </c>
       <c r="H49" s="3">
-        <v>311400</v>
+        <v>44700</v>
       </c>
       <c r="I49" s="3">
-        <v>311400</v>
+        <v>45300</v>
       </c>
       <c r="J49" s="3">
-        <v>311400</v>
+        <v>47900</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2370,19 +2370,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>63200</v>
+        <v>8900</v>
       </c>
       <c r="E52" s="3">
-        <v>10900</v>
+        <v>1600</v>
       </c>
       <c r="F52" s="3">
-        <v>26600</v>
+        <v>4200</v>
       </c>
       <c r="G52" s="3">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="H52" s="3">
-        <v>18300</v>
+        <v>2600</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2454,25 +2454,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2613000</v>
+        <v>368500</v>
       </c>
       <c r="E54" s="3">
-        <v>4073700</v>
+        <v>590600</v>
       </c>
       <c r="F54" s="3">
-        <v>5601200</v>
+        <v>881700</v>
       </c>
       <c r="G54" s="3">
-        <v>6333800</v>
+        <v>970200</v>
       </c>
       <c r="H54" s="3">
-        <v>1737600</v>
+        <v>249500</v>
       </c>
       <c r="I54" s="3">
-        <v>2375900</v>
+        <v>345500</v>
       </c>
       <c r="J54" s="3">
-        <v>1025300</v>
+        <v>157600</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2537,8 +2537,8 @@
       <c r="E57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F57" s="3">
-        <v>57400</v>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>30000</v>
+        <v>7300</v>
       </c>
       <c r="E58" s="3">
-        <v>19000</v>
+        <v>6200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H58" s="3">
-        <v>50000</v>
+        <v>8200</v>
       </c>
       <c r="I58" s="3">
-        <v>80000</v>
+        <v>11600</v>
       </c>
       <c r="J58" s="3">
-        <v>99000</v>
+        <v>15200</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>381800</v>
+        <v>1800</v>
       </c>
       <c r="E59" s="3">
-        <v>739200</v>
+        <v>3200</v>
       </c>
       <c r="F59" s="3">
-        <v>566600</v>
+        <v>1100</v>
       </c>
       <c r="G59" s="3">
-        <v>576100</v>
+        <v>21600</v>
       </c>
       <c r="H59" s="3">
-        <v>538500</v>
+        <v>41900</v>
       </c>
       <c r="I59" s="3">
-        <v>266200</v>
+        <v>28900</v>
       </c>
       <c r="J59" s="3">
-        <v>96100</v>
+        <v>12900</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2658,25 +2658,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>411800</v>
+        <v>58100</v>
       </c>
       <c r="E60" s="3">
-        <v>758200</v>
+        <v>109900</v>
       </c>
       <c r="F60" s="3">
-        <v>624000</v>
+        <v>98200</v>
       </c>
       <c r="G60" s="3">
-        <v>576100</v>
+        <v>88200</v>
       </c>
       <c r="H60" s="3">
-        <v>588500</v>
+        <v>84500</v>
       </c>
       <c r="I60" s="3">
-        <v>346200</v>
+        <v>50300</v>
       </c>
       <c r="J60" s="3">
-        <v>195100</v>
+        <v>30000</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2700,25 +2700,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>58900</v>
+        <v>3300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H61" s="3">
-        <v>68200</v>
+        <v>10900</v>
       </c>
       <c r="I61" s="3">
-        <v>67000</v>
+        <v>9700</v>
       </c>
       <c r="J61" s="3">
-        <v>114000</v>
+        <v>17500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>424100</v>
+        <v>23700</v>
       </c>
       <c r="E62" s="3">
-        <v>405600</v>
+        <v>15300</v>
       </c>
       <c r="F62" s="3">
-        <v>417600</v>
+        <v>17600</v>
       </c>
       <c r="G62" s="3">
-        <v>130500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>11400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>19100</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2910,25 +2910,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>894800</v>
+        <v>126200</v>
       </c>
       <c r="E66" s="3">
-        <v>1163800</v>
+        <v>168700</v>
       </c>
       <c r="F66" s="3">
-        <v>1041600</v>
+        <v>164000</v>
       </c>
       <c r="G66" s="3">
-        <v>706600</v>
+        <v>108200</v>
       </c>
       <c r="H66" s="3">
-        <v>668100</v>
+        <v>95900</v>
       </c>
       <c r="I66" s="3">
-        <v>415700</v>
+        <v>60400</v>
       </c>
       <c r="J66" s="3">
-        <v>614900</v>
+        <v>47500</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -3066,13 +3066,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>3104200</v>
+        <v>445800</v>
       </c>
       <c r="I70" s="3">
-        <v>2915400</v>
+        <v>423900</v>
       </c>
       <c r="J70" s="3">
-        <v>710300</v>
+        <v>109200</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3138,25 +3138,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-8327800</v>
+        <v>-1174400</v>
       </c>
       <c r="E72" s="3">
-        <v>-6862100</v>
+        <v>-994900</v>
       </c>
       <c r="F72" s="3">
-        <v>-4354800</v>
+        <v>-685500</v>
       </c>
       <c r="G72" s="3">
-        <v>-2023300</v>
+        <v>-309900</v>
       </c>
       <c r="H72" s="3">
-        <v>-2494200</v>
+        <v>-358200</v>
       </c>
       <c r="I72" s="3">
-        <v>-1014500</v>
+        <v>-147500</v>
       </c>
       <c r="J72" s="3">
-        <v>-357900</v>
+        <v>-55000</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3306,25 +3306,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1718200</v>
+        <v>242300</v>
       </c>
       <c r="E76" s="3">
-        <v>2909900</v>
+        <v>421900</v>
       </c>
       <c r="F76" s="3">
-        <v>4559600</v>
+        <v>717700</v>
       </c>
       <c r="G76" s="3">
-        <v>5627100</v>
+        <v>861900</v>
       </c>
       <c r="H76" s="3">
-        <v>-2034700</v>
+        <v>-292200</v>
       </c>
       <c r="I76" s="3">
-        <v>-955100</v>
+        <v>-138900</v>
       </c>
       <c r="J76" s="3">
-        <v>-299800</v>
+        <v>-46100</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3437,25 +3437,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1465700</v>
+        <v>-206700</v>
       </c>
       <c r="E81" s="3">
-        <v>-2507300</v>
+        <v>-363500</v>
       </c>
       <c r="F81" s="3">
-        <v>-2331500</v>
+        <v>-367000</v>
       </c>
       <c r="G81" s="3">
-        <v>470900</v>
+        <v>72100</v>
       </c>
       <c r="H81" s="3">
-        <v>-1485000</v>
+        <v>-208500</v>
       </c>
       <c r="I81" s="3">
-        <v>-402800</v>
+        <v>-58600</v>
       </c>
       <c r="J81" s="3">
-        <v>-298200</v>
+        <v>-45800</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3497,25 +3497,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>24700</v>
+        <v>7000</v>
       </c>
       <c r="E83" s="3">
-        <v>26100</v>
+        <v>8700</v>
       </c>
       <c r="F83" s="3">
-        <v>14600</v>
+        <v>4800</v>
       </c>
       <c r="G83" s="3">
-        <v>14300</v>
+        <v>3200</v>
       </c>
       <c r="H83" s="3">
-        <v>9800</v>
+        <v>2200</v>
       </c>
       <c r="I83" s="3">
-        <v>6700</v>
+        <v>1000</v>
       </c>
       <c r="J83" s="3">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3749,25 +3749,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1305000</v>
+        <v>-184000</v>
       </c>
       <c r="E89" s="3">
-        <v>-1102800</v>
+        <v>-159900</v>
       </c>
       <c r="F89" s="3">
-        <v>-973100</v>
+        <v>-153200</v>
       </c>
       <c r="G89" s="3">
-        <v>433600</v>
+        <v>66400</v>
       </c>
       <c r="H89" s="3">
-        <v>-868000</v>
+        <v>-124700</v>
       </c>
       <c r="I89" s="3">
-        <v>-280700</v>
+        <v>-40800</v>
       </c>
       <c r="J89" s="3">
-        <v>-252200</v>
+        <v>-38800</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3809,25 +3809,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-11400</v>
+        <v>-1600</v>
       </c>
       <c r="E91" s="3">
-        <v>-45800</v>
+        <v>-6600</v>
       </c>
       <c r="F91" s="3">
-        <v>-29900</v>
+        <v>-4700</v>
       </c>
       <c r="G91" s="3">
-        <v>-8000</v>
+        <v>-1200</v>
       </c>
       <c r="H91" s="3">
-        <v>-12200</v>
+        <v>-1800</v>
       </c>
       <c r="I91" s="3">
-        <v>-14400</v>
+        <v>-2100</v>
       </c>
       <c r="J91" s="3">
-        <v>-20300</v>
+        <v>-3100</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3935,25 +3935,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>102500</v>
+        <v>14500</v>
       </c>
       <c r="E94" s="3">
-        <v>458400</v>
+        <v>66500</v>
       </c>
       <c r="F94" s="3">
-        <v>-727200</v>
+        <v>-114500</v>
       </c>
       <c r="G94" s="3">
-        <v>-201900</v>
+        <v>-30900</v>
       </c>
       <c r="H94" s="3">
-        <v>212500</v>
+        <v>30500</v>
       </c>
       <c r="I94" s="3">
-        <v>9500</v>
+        <v>1400</v>
       </c>
       <c r="J94" s="3">
-        <v>-157700</v>
+        <v>-24200</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -4163,25 +4163,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>7600</v>
+        <v>1100</v>
       </c>
       <c r="E100" s="3">
-        <v>42400</v>
+        <v>6100</v>
       </c>
       <c r="F100" s="3">
-        <v>593900</v>
+        <v>93500</v>
       </c>
       <c r="G100" s="3">
-        <v>3440500</v>
+        <v>527000</v>
       </c>
       <c r="H100" s="3">
-        <v>152700</v>
+        <v>21900</v>
       </c>
       <c r="I100" s="3">
-        <v>1479700</v>
+        <v>215100</v>
       </c>
       <c r="J100" s="3">
-        <v>758600</v>
+        <v>116600</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -4205,25 +4205,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>84500</v>
+        <v>11900</v>
       </c>
       <c r="E101" s="3">
-        <v>389200</v>
+        <v>56400</v>
       </c>
       <c r="F101" s="3">
-        <v>-128800</v>
+        <v>-20300</v>
       </c>
       <c r="G101" s="3">
-        <v>-106600</v>
+        <v>-16300</v>
       </c>
       <c r="H101" s="3">
-        <v>15200</v>
+        <v>2200</v>
       </c>
       <c r="I101" s="3">
-        <v>59800</v>
+        <v>8700</v>
       </c>
       <c r="J101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -4247,25 +4247,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1110400</v>
+        <v>-156600</v>
       </c>
       <c r="E102" s="3">
-        <v>-212900</v>
+        <v>-30900</v>
       </c>
       <c r="F102" s="3">
-        <v>-1235100</v>
+        <v>-194400</v>
       </c>
       <c r="G102" s="3">
-        <v>3565500</v>
+        <v>546100</v>
       </c>
       <c r="H102" s="3">
-        <v>-487600</v>
+        <v>-70000</v>
       </c>
       <c r="I102" s="3">
-        <v>1268200</v>
+        <v>184400</v>
       </c>
       <c r="J102" s="3">
-        <v>348600</v>
+        <v>53600</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/IMAB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IMAB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>IMAB</t>
   </si>
@@ -656,55 +656,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,36 +717,39 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>3900</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>600</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>13900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>236300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1800</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,24 +762,27 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="3">
-        <v>3900</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3">
         <v>7300</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,36 +807,39 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>3900</v>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E10" s="3">
-        <v>-36100</v>
+        <v>600</v>
       </c>
       <c r="F10" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G10" s="3">
         <v>6500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>236300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,35 +874,36 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>114300</v>
+        <v>21800</v>
       </c>
       <c r="E12" s="3">
-        <v>131200</v>
+        <v>21400</v>
       </c>
       <c r="F12" s="3">
+        <v>22500</v>
+      </c>
+      <c r="G12" s="3">
         <v>190900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>150800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>120700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>61900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>41000</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,33 +961,36 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>20300</v>
+        <v>1200</v>
       </c>
       <c r="E14" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F14" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>-4800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-64200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -984,39 +1003,42 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3400</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>3700</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3">
+        <v>200</v>
+      </c>
+      <c r="G15" s="3">
         <v>2200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,35 +1070,36 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>178200</v>
+        <v>51400</v>
       </c>
       <c r="E17" s="3">
-        <v>253400</v>
+        <v>49600</v>
       </c>
       <c r="F17" s="3">
+        <v>51500</v>
+      </c>
+      <c r="G17" s="3">
         <v>339900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>212500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>214700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>71600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>45000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,36 +1112,39 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-174300</v>
+        <v>-51400</v>
       </c>
       <c r="E18" s="3">
-        <v>-285500</v>
+        <v>-49000</v>
       </c>
       <c r="F18" s="3">
+        <v>-53100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-326100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>23800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-210400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-63800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-43200</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1128,9 +1157,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,35 +1179,36 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>19300</v>
+        <v>4500</v>
       </c>
       <c r="E20" s="3">
-        <v>79800</v>
+        <v>19500</v>
       </c>
       <c r="F20" s="3">
+        <v>93000</v>
+      </c>
+      <c r="G20" s="3">
         <v>49600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>17600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,36 +1221,39 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-190200</v>
+        <v>-55700</v>
       </c>
       <c r="E21" s="3">
-        <v>-361700</v>
+        <v>-68000</v>
       </c>
       <c r="F21" s="3">
+        <v>-145800</v>
+      </c>
+      <c r="G21" s="3">
         <v>-373500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-207900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-54400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-45700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,36 +1266,39 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1272,36 +1311,39 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-206700</v>
+        <v>-49700</v>
       </c>
       <c r="E23" s="3">
-        <v>-363400</v>
+        <v>-82200</v>
       </c>
       <c r="F23" s="3">
+        <v>-141100</v>
+      </c>
+      <c r="G23" s="3">
         <v>-367500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>74000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-208500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-58300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-45800</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,33 +1356,36 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1900</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1401,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,36 +1446,39 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-206700</v>
+        <v>-49700</v>
       </c>
       <c r="E26" s="3">
-        <v>-363500</v>
+        <v>-82200</v>
       </c>
       <c r="F26" s="3">
+        <v>-141200</v>
+      </c>
+      <c r="G26" s="3">
         <v>-367000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>72100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-208500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-58600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-45800</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,36 +1491,39 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-206700</v>
+        <v>-22200</v>
       </c>
       <c r="E27" s="3">
-        <v>-363500</v>
+        <v>-207700</v>
       </c>
       <c r="F27" s="3">
+        <v>-371100</v>
+      </c>
+      <c r="G27" s="3">
         <v>-367000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>72100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-213300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-58600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-45800</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1536,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,20 +1581,23 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>27500</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-125500</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>-229900</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,36 +1716,39 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-19300</v>
+        <v>-4500</v>
       </c>
       <c r="E32" s="3">
-        <v>-79800</v>
+        <v>-19500</v>
       </c>
       <c r="F32" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-49600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-17600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1692,36 +1761,39 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-206700</v>
+        <v>-22200</v>
       </c>
       <c r="E33" s="3">
-        <v>-363500</v>
+        <v>-207700</v>
       </c>
       <c r="F33" s="3">
+        <v>-371100</v>
+      </c>
+      <c r="G33" s="3">
         <v>-367000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>72100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-208500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-58600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-45800</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1806,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,36 +1851,39 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-206700</v>
+        <v>-22200</v>
       </c>
       <c r="E35" s="3">
-        <v>-363500</v>
+        <v>-207700</v>
       </c>
       <c r="F35" s="3">
+        <v>-371100</v>
+      </c>
+      <c r="G35" s="3">
         <v>-367000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>72100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-208500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-58600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-45800</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,41 +1896,44 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1946,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,35 +1987,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>302000</v>
+        <v>68300</v>
       </c>
       <c r="E41" s="3">
+        <v>291500</v>
+      </c>
+      <c r="F41" s="3">
         <v>466000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>554700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>728900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>163400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>230900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>47300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,36 +2029,39 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>20900</v>
+        <v>105100</v>
       </c>
       <c r="E42" s="3">
+        <v>20200</v>
+      </c>
+      <c r="F42" s="3">
         <v>34800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>118600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>31300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>40900</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1985,36 +2074,39 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="E43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F43" s="3">
         <v>4800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>61200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>71400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,9 +2119,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2039,12 +2134,12 @@
       <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3">
         <v>4300</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2060,8 +2155,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2069,36 +2164,39 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="E45" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F45" s="3">
         <v>4800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,36 +2209,39 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>329500</v>
+        <v>176700</v>
       </c>
       <c r="E46" s="3">
+        <v>329900</v>
+      </c>
+      <c r="F46" s="3">
         <v>525800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>752700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>818500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>195500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>296200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>106300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2153,27 +2254,30 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1700</v>
-      </c>
-      <c r="E47" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>4500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>55400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>101800</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,42 +2293,45 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>11700</v>
+        <v>3800</v>
       </c>
       <c r="E48" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F48" s="3">
         <v>18000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3400</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,36 +2344,39 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>16700</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>40800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>44400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>43400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>44700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>45300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>47900</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,30 +2479,33 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8900</v>
+        <v>1400</v>
       </c>
       <c r="E52" s="3">
+        <v>33500</v>
+      </c>
+      <c r="F52" s="3">
         <v>1600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2600</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2402,12 +2521,15 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,36 +2569,39 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>368500</v>
+        <v>212700</v>
       </c>
       <c r="E54" s="3">
+        <v>368900</v>
+      </c>
+      <c r="F54" s="3">
         <v>590600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>881700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>970200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>249500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>345500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>157600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2614,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,8 +2655,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2558,8 +2688,8 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -2567,36 +2697,39 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7300</v>
+        <v>800</v>
       </c>
       <c r="E58" s="3">
+        <v>600</v>
+      </c>
+      <c r="F58" s="3">
         <v>6200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,36 +2742,39 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
+        <v>50900</v>
+      </c>
+      <c r="F59" s="3">
         <v>3200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>41900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12900</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,36 +2787,39 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E60" s="3">
         <v>58100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>109900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>98200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>88200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>84500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>50300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,36 +2832,39 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E61" s="3">
         <v>3300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2735,27 +2877,30 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>23700</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E62" s="3">
+        <v>64900</v>
+      </c>
+      <c r="F62" s="3">
         <v>15300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>19100</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,36 +3057,39 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>126200</v>
+        <v>11500</v>
       </c>
       <c r="E66" s="3">
+        <v>126300</v>
+      </c>
+      <c r="F66" s="3">
         <v>168700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>164000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>108200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>95900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>60400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47500</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3066,17 +3233,17 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>445800</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>423900</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>109200</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,36 +3301,39 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1174400</v>
+        <v>-1286000</v>
       </c>
       <c r="E72" s="3">
+        <v>-1263800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-994900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-685500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-309900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-358200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-147500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-55000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,36 +3481,39 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>242300</v>
+        <v>201200</v>
       </c>
       <c r="E76" s="3">
+        <v>242600</v>
+      </c>
+      <c r="F76" s="3">
         <v>421900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>717700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>861900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-292200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-138900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-46100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3526,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,41 +3571,44 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,36 +3621,39 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-206700</v>
+        <v>-22200</v>
       </c>
       <c r="E81" s="3">
-        <v>-363500</v>
+        <v>-207700</v>
       </c>
       <c r="F81" s="3">
+        <v>-371100</v>
+      </c>
+      <c r="G81" s="3">
         <v>-367000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>72100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-208500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-58600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-45800</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3666,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,35 +3688,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
-        <v>8700</v>
+        <v>1100</v>
       </c>
       <c r="F83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G83" s="3">
         <v>4800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,36 +3955,39 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-184000</v>
+        <v>-52700</v>
       </c>
       <c r="E89" s="3">
-        <v>-159900</v>
+        <v>-72700</v>
       </c>
       <c r="F89" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="G89" s="3">
         <v>-153200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>66400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-124700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-40800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-38800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4000,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,35 +4022,36 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-6600</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-4700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4064,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,36 +4154,39 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>14500</v>
+        <v>-136000</v>
       </c>
       <c r="E94" s="3">
-        <v>66500</v>
+        <v>-15200</v>
       </c>
       <c r="F94" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-114500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-30900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>30500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4199,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,36 +4398,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1100</v>
+        <v>-300</v>
       </c>
       <c r="E100" s="3">
-        <v>6100</v>
+        <v>-8200</v>
       </c>
       <c r="F100" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G100" s="3">
         <v>93500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>527000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>21900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>215100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>116600</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,35 +4443,38 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>11900</v>
+        <v>600</v>
       </c>
       <c r="E101" s="3">
-        <v>56400</v>
+        <v>5200</v>
       </c>
       <c r="F101" s="3">
+        <v>14200</v>
+      </c>
+      <c r="G101" s="3">
         <v>-20300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-16300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8700</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -4240,36 +4488,39 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-156600</v>
+        <v>-188400</v>
       </c>
       <c r="E102" s="3">
-        <v>-30900</v>
+        <v>-90900</v>
       </c>
       <c r="F102" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="G102" s="3">
         <v>-194400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>546100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-70000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>184400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>53600</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4533,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
